--- a/Agile/Unit_Test_Plan_v0.1.xlsx
+++ b/Agile/Unit_Test_Plan_v0.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://infosystechnologies-my.sharepoint.com/personal/kamaljeet_kaur01_ad_infosys_com1/Documents/Infosys/CC/Events/Oct 2021 - Mar 2022/CC2.0/Internship/Jan-Apr 2022/Artifacts/internship/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8abbb0155c994d04/Desktop/AI_Response_Validation_System/Agile/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B9D4FEA-5A3F-460B-9A40-165575443B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{3B9D4FEA-5A3F-460B-9A40-165575443B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1BB9D73-AB79-4424-8B85-54C833EE0FFC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
+    <workbookView xWindow="10116" yWindow="5112" windowWidth="12420" windowHeight="8880" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
   <sheets>
     <sheet name="UT" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Actual Result</t>
   </si>
@@ -52,6 +52,93 @@
   </si>
   <si>
     <t>Sl: No:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valid Evaluation input </t>
+  </si>
+  <si>
+    <t>Enter a Valid question and AI response and click Validation</t>
+  </si>
+  <si>
+    <t>Valid question and response are provided</t>
+  </si>
+  <si>
+    <t>Evaluation be processrd succesfully</t>
+  </si>
+  <si>
+    <t>Evaluation processe successfully</t>
+  </si>
+  <si>
+    <t>Error message displayed</t>
+  </si>
+  <si>
+    <t>System should display an error asking the user to enter the question</t>
+  </si>
+  <si>
+    <t>Question is blank</t>
+  </si>
+  <si>
+    <t>Leave the User Question field empty and click Validate</t>
+  </si>
+  <si>
+    <t>Empty AI Response Validation</t>
+  </si>
+  <si>
+    <t>Optional Reference Input</t>
+  </si>
+  <si>
+    <t>Enter a question but leave AI Response empty and click Validate</t>
+  </si>
+  <si>
+    <t>AI response is blank</t>
+  </si>
+  <si>
+    <t>Empty AI Response validation</t>
+  </si>
+  <si>
+    <t>Enter a question but leave AI Response empty and click validation</t>
+  </si>
+  <si>
+    <t>Reference feils is empty</t>
+  </si>
+  <si>
+    <t>System should display an error asking the user to enter the AI response</t>
+  </si>
+  <si>
+    <t>System should still allow evaluation</t>
+  </si>
+  <si>
+    <t>Evaluation request processed</t>
+  </si>
+  <si>
+    <t>Relavance Evaluation</t>
+  </si>
+  <si>
+    <t>Eneter a question an an Ai response related to the question</t>
+  </si>
+  <si>
+    <t>Response is relevant to the question</t>
+  </si>
+  <si>
+    <t>Relevance score should be high</t>
+  </si>
+  <si>
+    <t>Relavance evaluation completed</t>
+  </si>
+  <si>
+    <t>API returned successful response</t>
+  </si>
+  <si>
+    <t>API should return successful evaluation response</t>
+  </si>
+  <si>
+    <t>Backend API is running</t>
+  </si>
+  <si>
+    <t>Submit vaild data through the UI</t>
+  </si>
+  <si>
+    <t>API Evaluation</t>
   </si>
 </sst>
 </file>
@@ -94,7 +181,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -117,16 +204,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -147,9 +251,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -187,7 +291,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -293,7 +397,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -435,7 +539,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -443,17 +547,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="5" width="16.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="4" max="5" width="16.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -473,45 +577,125 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+    <row r="2" spans="1:6" ht="78" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+    <row r="3" spans="1:6" ht="78" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+    <row r="4" spans="1:6" ht="93.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+    <row r="5" spans="1:6" ht="93.6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+    <row r="6" spans="1:6" ht="78" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="78" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Agile/Unit_Test_Plan_v0.1.xlsx
+++ b/Agile/Unit_Test_Plan_v0.1.xlsx
@@ -1,182 +1,65 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8abbb0155c994d04/Desktop/AI_Response_Validation_System/Agile/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{3B9D4FEA-5A3F-460B-9A40-165575443B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1BB9D73-AB79-4424-8B85-54C833EE0FFC}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10116" yWindow="5112" windowWidth="12420" windowHeight="8880" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="10200" yWindow="0" windowWidth="12936" windowHeight="12336" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="UT" sheetId="1" r:id="rId1"/>
+    <sheet name="UT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
-  <si>
-    <t>Actual Result</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
-    <t>Condition to be tested</t>
-  </si>
-  <si>
-    <t>Test Procedure</t>
-  </si>
-  <si>
-    <t>Test Case Name</t>
-  </si>
-  <si>
-    <t>Sl: No:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid Evaluation input </t>
-  </si>
-  <si>
-    <t>Enter a Valid question and AI response and click Validation</t>
-  </si>
-  <si>
-    <t>Valid question and response are provided</t>
-  </si>
-  <si>
-    <t>Evaluation be processrd succesfully</t>
-  </si>
-  <si>
-    <t>Evaluation processe successfully</t>
-  </si>
-  <si>
-    <t>Error message displayed</t>
-  </si>
-  <si>
-    <t>System should display an error asking the user to enter the question</t>
-  </si>
-  <si>
-    <t>Question is blank</t>
-  </si>
-  <si>
-    <t>Leave the User Question field empty and click Validate</t>
-  </si>
-  <si>
-    <t>Empty AI Response Validation</t>
-  </si>
-  <si>
-    <t>Optional Reference Input</t>
-  </si>
-  <si>
-    <t>Enter a question but leave AI Response empty and click Validate</t>
-  </si>
-  <si>
-    <t>AI response is blank</t>
-  </si>
-  <si>
-    <t>Empty AI Response validation</t>
-  </si>
-  <si>
-    <t>Enter a question but leave AI Response empty and click validation</t>
-  </si>
-  <si>
-    <t>Reference feils is empty</t>
-  </si>
-  <si>
-    <t>System should display an error asking the user to enter the AI response</t>
-  </si>
-  <si>
-    <t>System should still allow evaluation</t>
-  </si>
-  <si>
-    <t>Evaluation request processed</t>
-  </si>
-  <si>
-    <t>Relavance Evaluation</t>
-  </si>
-  <si>
-    <t>Eneter a question an an Ai response related to the question</t>
-  </si>
-  <si>
-    <t>Response is relevant to the question</t>
-  </si>
-  <si>
-    <t>Relevance score should be high</t>
-  </si>
-  <si>
-    <t>Relavance evaluation completed</t>
-  </si>
-  <si>
-    <t>API returned successful response</t>
-  </si>
-  <si>
-    <t>API should return successful evaluation response</t>
-  </si>
-  <si>
-    <t>Backend API is running</t>
-  </si>
-  <si>
-    <t>Submit vaild data through the UI</t>
-  </si>
-  <si>
-    <t>API Evaluation</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="56"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color indexed="56"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.39997558519241921"/>
+        <fgColor theme="3" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -219,34 +102,123 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -546,159 +518,596 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="9.109375" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="5" width="16.5546875" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" customWidth="1"/>
+    <col width="9.109375" customWidth="1" min="1" max="1"/>
+    <col width="14.33203125" customWidth="1" style="11" min="2" max="2"/>
+    <col width="15" customWidth="1" style="13" min="3" max="3"/>
+    <col width="16.5546875" customWidth="1" style="12" min="4" max="4"/>
+    <col width="16.5546875" customWidth="1" style="8" min="5" max="5"/>
+    <col width="15.88671875" customWidth="1" style="8" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="31.2" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Sl: No:</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Test Case Name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Test Procedure</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Condition to be tested</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="78" customHeight="1">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valid Evaluation input </t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Enter a Valid question and AI response and click Validation</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Valid question and response are provided</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Evaluation be processrd succesfully</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Evaluation processe successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="78" customHeight="1">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Empty AI Response Validation</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Leave the User Question field empty and click Validate</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Question is blank</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>System should display an error asking the user to enter the question</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Error message displayed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="93.59999999999999" customHeight="1">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Empty AI Response validation</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Enter a question but leave AI Response empty and click validation</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>AI response is blank</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>System should display an error asking the user to enter the AI response</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Error message displayed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="93.59999999999999" customHeight="1">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Optional Reference Input</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Enter a question but leave AI Response empty and click Validate</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Reference feils is empty</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>System should still allow evaluation</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Evaluation request processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="78" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Relavance Evaluation</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Eneter a question an an Ai response related to the question</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Response is relevant to the question</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Relevance score should be high</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Relavance evaluation completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="78" customHeight="1">
+      <c r="A7" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>API Evaluation</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Submit vaild data through the UI</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Backend API is running</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>API should return successful evaluation response</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>API returned successful response</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="93.59999999999999" customHeight="1">
+      <c r="A8" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>M2.1-Fully Relavant Response</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Enter a question and a directly relevant AI response, then click Validate.</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Question: What is the capital of India? Response: The capital of India is New Delhi.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Relevance score should be high and response should be classified as Fully Relevant.</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Relavance Score:81.6%. Response was strongly relevant</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46.8" customHeight="1">
+      <c r="A9" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>M2.1-Partially Relevant Response</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Enter a question and a related but incomplete AI response,then click vlidate</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question:What  are the benifts of regular exercise? Response: Regular exercise is good for your health. </t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Response should be identified as relevant but not fully addressing the question.</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Relevance score: 69.5%. Response was classified as Mostly Relevant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="156" customHeight="1">
+      <c r="A10" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>M2.1 - Off-Topic Response</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Enter a question and an unrelated AI response, then click Validate.</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Question: What is the capital of India? Response: Python is a programming language used to build software applications.</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Relevance score should be low and response should be classified as Off-Topic.</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Relevance score: 6.6%. Response was classified as Off-Topic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="140.4" customFormat="1" customHeight="1" s="10">
+      <c r="A11" s="14" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="78" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>M2.2-Correct response</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Enter a question, correct AI response, and matching reference answer, then click Validate.</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Question: What is the capital of France? Response: The capital of France is Paris. Reference: Paris is the capital city of France.</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Accuracy score should be high and the response should be classified as Correct.</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Accuracy score: 82.5%. The AI response was strongly supported by the reference answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="156" customFormat="1" customHeight="1" s="10">
+      <c r="A12" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>M2.2 - Incorrect/Contradictory Response</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Enter a question, incorrect AI response, and reference answer, then click Validate.</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Question: What is the capital of France? Response: The capital of France is London. Reference: Paris is the capital city of France.</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Accuracy score should be 0% and the response should be classified as Incorrect because it contradicts the reference answer.</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Accuracy score: 0.0%. The response was identified as contradictory to the retrieved evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="296.4" customFormat="1" customHeight="1" s="4">
+      <c r="A13" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>M2.2 - Partially Correct Response</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Enter a question, partially correct AI response, and reference answer, then click Validate.</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Question: What are the benefits of regular exercise? Response: Regular exercise helps improve physical health. Reference: Regular exercise improves physical health, strengthens muscles, supports mental health, and reduces the risk of chronic diseases.</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>The response should receive a moderate accuracy score and be classified as Mostly Correct.</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Accuracy score: 74.4%. The response was classified as Mostly Correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="140.4" customFormat="1" customHeight="1" s="10">
+      <c r="A14" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>M2.3 - Hallucinated/Contradictory Response</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Enter a question, contradictory AI response, and reference evidence, then click Validate.</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Question: What is the capital of France? Response: The capital of France is London. Reference: Paris is the capital city of France.</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Hallucination safety should be very low and the system should identify the contradictory information as a hallucination.</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Hallucination safety: 0.0%. The response was identified as contradicting the available evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="140.4" customFormat="1" customHeight="1" s="10">
+      <c r="A15" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>M2.3 - Supported Response</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Enter a question, evidence-supported AI response, and reference evidence, then click Validate.</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Question: What is the capital of France? Response: The capital of France is Paris. Reference: Paris is the capital city of France.</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Hallucination safety should be high and the response should be identified as well supported by the evidence.</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Hallucination safety: 98.2%. The response was well supported by the available evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="93.6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>M2.4 - Benchmark Evaluation Set</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Run the Milestone 2 evaluation dataset through the Relevance, Accuracy, and Hallucination agents.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Representative cases covering correct, incorrect, partially correct, irrelevant, incomplete, unsupported, and contradictory responses.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>All three agents should process every benchmark case successfully.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>M2.4 evaluation completed successfully using 7 representative cases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>M2.4 - Agent Consistency</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Compare agent scores and categories across the same benchmark evaluation cases.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Multiple QA cases are evaluated consistently by the Relevance, Accuracy, and Hallucination agents.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Scores must remain within the valid 0 to 1 range and expected behaviors should be identified correctly.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>M2.4 consistency tests passed for all benchmark cases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>M2.4 - Unsupported Claim Detection</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Evaluate a response containing one supported claim and one unsupported claim.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Response: The capital of France is Paris. France has 20 states. Evidence: Paris is the capital city of France.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>The system should identify the specific unsupported claim and provide supporting evidence and reasoning.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Unsupported claim 'France has 20 states.' was identified with evidence and reasoning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="93.6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="78" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="78" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>30</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>M2.4 - Full Regression Test</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Run the complete pytest test suite after Milestone 2 implementation.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>All existing Milestone 1 and Milestone 2 functionality is tested together.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>All automated tests should pass without functional failures.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>19 tests passed successfully. 4 deprecation warnings were reported.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" scale="88"/>
 </worksheet>
 </file>